--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>business_date</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>Tarreessaa Wadaajoo</t>
+  </si>
+  <si>
+    <t>Baay`isaa Kabbadaa</t>
   </si>
 </sst>
 </file>
@@ -937,10 +940,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1633,6 +1637,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>46270</v>
+      </c>
+      <c r="B31">
+        <v>1030</v>
+      </c>
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31">
+        <v>1000</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>69000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>business_date</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>Baay`isaa Kabbadaa</t>
+  </si>
+  <si>
+    <t>Mul`ataa Qajeelaa</t>
   </si>
 </sst>
 </file>
@@ -940,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1657,6 +1660,29 @@
         <v>69000</v>
       </c>
     </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B32">
+        <v>1031</v>
+      </c>
+      <c r="C32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>69000</v>
+      </c>
+      <c r="G32">
+        <v>40000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1407,7 +1407,7 @@
         <v>69000</v>
       </c>
       <c r="G20">
-        <v>1000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>business_date</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>Mul`ataa Qajeelaa</t>
+  </si>
+  <si>
+    <t>Wasihun Geletu</t>
   </si>
 </sst>
 </file>
@@ -943,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1683,6 +1686,29 @@
         <v>40000</v>
       </c>
     </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B33">
+        <v>1032</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>69000</v>
+      </c>
+      <c r="G33">
+        <v>3000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -951,6 +951,7 @@
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1479,7 +1480,7 @@
         <v>69000</v>
       </c>
       <c r="G23">
-        <v>1000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10332"/>
   </bookViews>
   <sheets>
     <sheet name="EGSA2026_27_Monthly_report" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>business_date</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>Wasihun Geletu</t>
+  </si>
+  <si>
+    <t>Galaa Yaalii</t>
   </si>
 </sst>
 </file>
@@ -946,7 +949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1710,6 +1713,29 @@
         <v>3000</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B34">
+        <v>1033</v>
+      </c>
+      <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>69000</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop from C\general\monthly-report\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10332"/>
+    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="EGSA2026_27_Monthly_report" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>business_date</t>
   </si>
@@ -111,9 +111,6 @@
     <t>Milkesa Gebre</t>
   </si>
   <si>
-    <t>NULL</t>
-  </si>
-  <si>
     <t>Worku Guta</t>
   </si>
   <si>
@@ -135,135 +132,23 @@
     <t>Baay`isaa Kabbadaa</t>
   </si>
   <si>
-    <t>Mul`ataa Qajeelaa</t>
-  </si>
-  <si>
     <t>Wasihun Geletu</t>
   </si>
   <si>
     <t>Galaa Yaalii</t>
+  </si>
+  <si>
+    <t>Mullataa Qajeelaa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -276,196 +161,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -474,207 +179,41 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -697,44 +236,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -767,9 +306,9 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -808,142 +347,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -952,47 +515,42 @@
   <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>46261</v>
-      </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
-        <v>1000</v>
-      </c>
       <c r="E2">
         <v>88893</v>
       </c>
@@ -1000,12 +558,12 @@
         <v>69000</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>46260</v>
+      <c r="A3" s="3">
+        <v>46286</v>
       </c>
       <c r="B3">
         <v>1002</v>
@@ -1023,12 +581,12 @@
         <v>69000</v>
       </c>
       <c r="G3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>46261</v>
+      <c r="A4" s="3">
+        <v>46291</v>
       </c>
       <c r="B4">
         <v>1003</v>
@@ -1046,22 +604,16 @@
         <v>69000</v>
       </c>
       <c r="G4">
-        <v>11000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>46260</v>
-      </c>
       <c r="B5">
         <v>1004</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5">
-        <v>1000</v>
-      </c>
       <c r="E5">
         <v>84553</v>
       </c>
@@ -1069,22 +621,16 @@
         <v>69000</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>46259</v>
-      </c>
       <c r="B6">
         <v>1005</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D6">
-        <v>1000</v>
-      </c>
       <c r="E6">
         <v>61406</v>
       </c>
@@ -1092,22 +638,16 @@
         <v>69000</v>
       </c>
       <c r="G6">
-        <v>11000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>46260</v>
-      </c>
       <c r="B7">
         <v>1006</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7">
-        <v>1000</v>
-      </c>
       <c r="E7">
         <v>151000</v>
       </c>
@@ -1115,22 +655,16 @@
         <v>69000</v>
       </c>
       <c r="G7">
-        <v>11000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>46262</v>
-      </c>
       <c r="B8">
         <v>1007</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D8">
-        <v>1000</v>
-      </c>
       <c r="E8">
         <v>59067</v>
       </c>
@@ -1138,12 +672,12 @@
         <v>69000</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>46258</v>
+      <c r="A9" s="3">
+        <v>46290</v>
       </c>
       <c r="B9">
         <v>1008</v>
@@ -1161,22 +695,16 @@
         <v>69000</v>
       </c>
       <c r="G9">
-        <v>11000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>46258</v>
-      </c>
       <c r="B10">
         <v>1009</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10">
-        <v>1000</v>
-      </c>
       <c r="E10">
         <v>61406</v>
       </c>
@@ -1184,12 +712,12 @@
         <v>69000</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>46261</v>
+      <c r="A11" s="3">
+        <v>46290</v>
       </c>
       <c r="B11">
         <v>1010</v>
@@ -1207,22 +735,16 @@
         <v>69000</v>
       </c>
       <c r="G11">
-        <v>21000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>46262</v>
-      </c>
       <c r="B12">
         <v>1011</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
-      <c r="D12">
-        <v>1000</v>
-      </c>
       <c r="E12">
         <v>59067</v>
       </c>
@@ -1230,22 +752,16 @@
         <v>69000</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
-        <v>46261</v>
-      </c>
       <c r="B13">
         <v>1012</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13">
-        <v>1000</v>
-      </c>
       <c r="E13">
         <v>153500</v>
       </c>
@@ -1253,12 +769,12 @@
         <v>69000</v>
       </c>
       <c r="G13">
-        <v>99000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
-        <v>46259</v>
+      <c r="A14" s="3">
+        <v>46290</v>
       </c>
       <c r="B14">
         <v>1013</v>
@@ -1276,22 +792,16 @@
         <v>69000</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>46265</v>
-      </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
-      <c r="D15">
-        <v>1000</v>
-      </c>
       <c r="E15">
         <v>102928</v>
       </c>
@@ -1299,22 +809,16 @@
         <v>69000</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>46263</v>
-      </c>
       <c r="B16">
         <v>1015</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
-      <c r="D16">
-        <v>1000</v>
-      </c>
       <c r="E16">
         <v>184553</v>
       </c>
@@ -1322,22 +826,16 @@
         <v>69000</v>
       </c>
       <c r="G16">
-        <v>101000</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>46265</v>
-      </c>
       <c r="B17">
         <v>1016</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
-      <c r="D17">
-        <v>1000</v>
-      </c>
       <c r="E17">
         <v>54973</v>
       </c>
@@ -1345,22 +843,16 @@
         <v>69000</v>
       </c>
       <c r="G17">
-        <v>15000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>46262</v>
-      </c>
       <c r="B18">
         <v>1017</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
-      <c r="D18">
-        <v>1000</v>
-      </c>
       <c r="E18">
         <v>73327</v>
       </c>
@@ -1368,12 +860,12 @@
         <v>69000</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>46260</v>
+      <c r="A19" s="3">
+        <v>46286</v>
       </c>
       <c r="B19">
         <v>1018</v>
@@ -1391,22 +883,16 @@
         <v>69000</v>
       </c>
       <c r="G19">
-        <v>74000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>46260</v>
-      </c>
       <c r="B20">
         <v>1019</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
-      <c r="D20">
-        <v>1000</v>
-      </c>
       <c r="E20">
         <v>0</v>
       </c>
@@ -1414,22 +900,16 @@
         <v>69000</v>
       </c>
       <c r="G20">
-        <v>42000</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
-        <v>46264</v>
-      </c>
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
-      <c r="D21">
-        <v>1000</v>
-      </c>
       <c r="E21">
         <v>51464</v>
       </c>
@@ -1437,12 +917,12 @@
         <v>69000</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>46258</v>
+      <c r="A22" s="3">
+        <v>46290</v>
       </c>
       <c r="B22">
         <v>1021</v>
@@ -1460,22 +940,16 @@
         <v>69000</v>
       </c>
       <c r="G22">
-        <v>40000</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
-        <v>46262</v>
-      </c>
       <c r="B23">
         <v>1022</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
-      <c r="D23">
-        <v>1000</v>
-      </c>
       <c r="E23">
         <v>65500</v>
       </c>
@@ -1483,22 +957,16 @@
         <v>69000</v>
       </c>
       <c r="G23">
-        <v>6000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>46263</v>
-      </c>
       <c r="B24">
         <v>1023</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="D24">
-        <v>1000</v>
-      </c>
       <c r="E24">
         <v>53803</v>
       </c>
@@ -1506,21 +974,15 @@
         <v>69000</v>
       </c>
       <c r="G24">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>30</v>
-      </c>
       <c r="B25">
         <v>1024</v>
       </c>
       <c r="C25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E25">
         <v>199000</v>
@@ -1533,17 +995,11 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>46263</v>
-      </c>
       <c r="B26">
         <v>1025</v>
       </c>
       <c r="C26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26">
-        <v>1000</v>
+        <v>31</v>
       </c>
       <c r="E26">
         <v>49125</v>
@@ -1552,21 +1008,15 @@
         <v>69000</v>
       </c>
       <c r="G26">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
-        <v>46263</v>
-      </c>
       <c r="B27">
         <v>1026</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="E27">
         <v>51464</v>
@@ -1575,18 +1025,18 @@
         <v>69000</v>
       </c>
       <c r="G27">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>46259</v>
+      <c r="A28" s="3">
+        <v>46291</v>
       </c>
       <c r="B28">
         <v>1027</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D28">
         <v>1000</v>
@@ -1598,18 +1048,18 @@
         <v>69000</v>
       </c>
       <c r="G28">
-        <v>41000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
-        <v>46261</v>
+      <c r="A29" s="3">
+        <v>46290</v>
       </c>
       <c r="B29">
         <v>1028</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D29">
         <v>1000</v>
@@ -1621,21 +1071,15 @@
         <v>69000</v>
       </c>
       <c r="G29">
-        <v>15000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>46265</v>
-      </c>
       <c r="B30">
         <v>1029</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30">
-        <v>1000</v>
+        <v>35</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1644,21 +1088,15 @@
         <v>69000</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
-        <v>46270</v>
-      </c>
       <c r="B31">
         <v>1030</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1666,19 +1104,22 @@
       <c r="F31">
         <v>69000</v>
       </c>
+      <c r="G31">
+        <v>1000</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>46274</v>
+      <c r="A32" s="3">
+        <v>46291</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1690,18 +1131,12 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
-        <v>46282</v>
-      </c>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1713,18 +1148,12 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <v>46286</v>
-      </c>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E34">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1071,7 +1071,7 @@
         <v>69000</v>
       </c>
       <c r="G29">
-        <v>16000</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -659,11 +659,17 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>46291</v>
+      </c>
       <c r="B8">
         <v>1007</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
+      </c>
+      <c r="D8">
+        <v>1000</v>
       </c>
       <c r="E8">
         <v>59067</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -516,7 +516,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.88671875" bestFit="1" customWidth="1"/>
   </cols>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -804,11 +804,17 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>46291</v>
+      </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
+      </c>
+      <c r="D15">
+        <v>1000</v>
       </c>
       <c r="E15">
         <v>102928</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -583,7 +583,7 @@
         <v>69000</v>
       </c>
       <c r="G3">
-        <v>2000</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -610,12 +610,18 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>46291</v>
+      </c>
       <c r="B5">
         <v>1004</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
+      <c r="D5">
+        <v>1000</v>
+      </c>
       <c r="E5">
         <v>84553</v>
       </c>
@@ -627,12 +633,18 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>46291</v>
+      </c>
       <c r="B6">
         <v>1005</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
       <c r="E6">
         <v>61406</v>
       </c>
@@ -644,11 +656,17 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>46291</v>
+      </c>
       <c r="B7">
         <v>1006</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
+      </c>
+      <c r="D7">
+        <v>1000</v>
       </c>
       <c r="E7">
         <v>151000</v>
@@ -901,11 +919,17 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>46291</v>
+      </c>
       <c r="B20">
         <v>1019</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
+      </c>
+      <c r="D20">
+        <v>1000</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1009,11 +1033,17 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>46291</v>
+      </c>
       <c r="B26">
         <v>1025</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
+      </c>
+      <c r="D26">
+        <v>1000</v>
       </c>
       <c r="E26">
         <v>49125</v>
@@ -1085,7 +1115,7 @@
         <v>69000</v>
       </c>
       <c r="G29">
-        <v>29000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1145,7 +1175,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>1032</v>
       </c>
@@ -1162,12 +1192,18 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>46291</v>
+      </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
         <v>38</v>
+      </c>
+      <c r="D34">
+        <v>1000</v>
       </c>
       <c r="E34">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -879,11 +879,17 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>46294</v>
+      </c>
       <c r="B18">
         <v>1017</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
+      </c>
+      <c r="D18">
+        <v>1000</v>
       </c>
       <c r="E18">
         <v>73327</v>
@@ -1056,11 +1062,17 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>46294</v>
+      </c>
       <c r="B27">
         <v>1026</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
+      </c>
+      <c r="D27">
+        <v>1000</v>
       </c>
       <c r="E27">
         <v>51464</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -845,12 +845,18 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>46295</v>
+      </c>
       <c r="B16">
         <v>1015</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
+      <c r="D16">
+        <v>1000</v>
+      </c>
       <c r="E16">
         <v>184553</v>
       </c>
@@ -858,7 +864,7 @@
         <v>69000</v>
       </c>
       <c r="G16">
-        <v>102000</v>
+        <v>103000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1005,11 +1011,17 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>46294</v>
+      </c>
       <c r="B24">
         <v>1023</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
+      </c>
+      <c r="D24">
+        <v>1000</v>
       </c>
       <c r="E24">
         <v>53803</v>
@@ -1131,12 +1143,18 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>46294</v>
+      </c>
       <c r="B30">
         <v>1029</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
+      <c r="D30">
+        <v>1000</v>
+      </c>
       <c r="E30">
         <v>0</v>
       </c>
@@ -1144,7 +1162,7 @@
         <v>69000</v>
       </c>
       <c r="G30">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1188,11 +1206,17 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <v>46294</v>
+      </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
         <v>37</v>
+      </c>
+      <c r="D33">
+        <v>1000</v>
       </c>
       <c r="E33">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -765,11 +765,17 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>46295</v>
+      </c>
       <c r="B12">
         <v>1011</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
+      </c>
+      <c r="D12">
+        <v>1000</v>
       </c>
       <c r="E12">
         <v>59067</v>
@@ -954,11 +960,17 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>46295</v>
+      </c>
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
+      </c>
+      <c r="D21">
+        <v>1000</v>
       </c>
       <c r="E21">
         <v>51464</v>
@@ -994,12 +1006,18 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>46282</v>
+      </c>
       <c r="B23">
         <v>1022</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
+      <c r="D23">
+        <v>1000</v>
+      </c>
       <c r="E23">
         <v>65500</v>
       </c>
@@ -1007,7 +1025,7 @@
         <v>69000</v>
       </c>
       <c r="G23">
-        <v>7000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>business_date</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>Mullataa Qajeelaa</t>
+  </si>
+  <si>
+    <t>9/302026</t>
   </si>
 </sst>
 </file>
@@ -547,11 +550,17 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>46295</v>
+      </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
       </c>
       <c r="E2">
         <v>88893</v>
@@ -725,11 +734,17 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>46295</v>
+      </c>
       <c r="B10">
         <v>1009</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
+      </c>
+      <c r="D10">
+        <v>1000</v>
       </c>
       <c r="E10">
         <v>61406</v>
@@ -788,11 +803,17 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>46295</v>
+      </c>
       <c r="B13">
         <v>1012</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
+      </c>
+      <c r="D13">
+        <v>1000</v>
       </c>
       <c r="E13">
         <v>153500</v>
@@ -1184,11 +1205,17 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="B31">
         <v>1030</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
+      </c>
+      <c r="D31">
+        <v>1000</v>
       </c>
       <c r="E31">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1073,12 +1073,18 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>46296</v>
+      </c>
       <c r="B25">
         <v>1024</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
+      <c r="D25">
+        <v>1000</v>
+      </c>
       <c r="E25">
         <v>199000</v>
       </c>
@@ -1086,7 +1092,7 @@
         <v>69000</v>
       </c>
       <c r="G25">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -895,11 +895,17 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>46296</v>
+      </c>
       <c r="B17">
         <v>1016</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
+      </c>
+      <c r="D17">
+        <v>1000</v>
       </c>
       <c r="E17">
         <v>54973</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -638,7 +638,7 @@
         <v>69000</v>
       </c>
       <c r="G5">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1213,7 +1213,7 @@
         <v>69000</v>
       </c>
       <c r="G30">
-        <v>2000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>business_date</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>Mullataa Qajeelaa</t>
-  </si>
-  <si>
-    <t>9/302026</t>
   </si>
 </sst>
 </file>
@@ -550,18 +547,12 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>46295</v>
-      </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
-        <v>1000</v>
-      </c>
       <c r="E2">
         <v>88893</v>
       </c>
@@ -569,22 +560,16 @@
         <v>69000</v>
       </c>
       <c r="G2">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>46286</v>
-      </c>
       <c r="B3">
         <v>1002</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3">
-        <v>1000</v>
-      </c>
       <c r="E3">
         <v>151000</v>
       </c>
@@ -592,22 +577,16 @@
         <v>69000</v>
       </c>
       <c r="G3">
-        <v>52000</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>46291</v>
-      </c>
       <c r="B4">
         <v>1003</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4">
-        <v>1000</v>
-      </c>
       <c r="E4">
         <v>151000</v>
       </c>
@@ -615,22 +594,16 @@
         <v>69000</v>
       </c>
       <c r="G4">
-        <v>12000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>46291</v>
-      </c>
       <c r="B5">
         <v>1004</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5">
-        <v>1000</v>
-      </c>
       <c r="E5">
         <v>84553</v>
       </c>
@@ -638,22 +611,16 @@
         <v>69000</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>46291</v>
-      </c>
       <c r="B6">
         <v>1005</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D6">
-        <v>1000</v>
-      </c>
       <c r="E6">
         <v>61406</v>
       </c>
@@ -661,22 +628,16 @@
         <v>69000</v>
       </c>
       <c r="G6">
-        <v>12000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>46291</v>
-      </c>
       <c r="B7">
         <v>1006</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7">
-        <v>1000</v>
-      </c>
       <c r="E7">
         <v>151000</v>
       </c>
@@ -684,22 +645,16 @@
         <v>69000</v>
       </c>
       <c r="G7">
-        <v>12000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>46291</v>
-      </c>
       <c r="B8">
         <v>1007</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D8">
-        <v>1000</v>
-      </c>
       <c r="E8">
         <v>59067</v>
       </c>
@@ -707,22 +662,16 @@
         <v>69000</v>
       </c>
       <c r="G8">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>46290</v>
-      </c>
       <c r="B9">
         <v>1008</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="D9">
-        <v>1000</v>
-      </c>
       <c r="E9">
         <v>145036</v>
       </c>
@@ -730,22 +679,16 @@
         <v>69000</v>
       </c>
       <c r="G9">
-        <v>12000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>46295</v>
-      </c>
       <c r="B10">
         <v>1009</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10">
-        <v>1000</v>
-      </c>
       <c r="E10">
         <v>61406</v>
       </c>
@@ -753,22 +696,16 @@
         <v>69000</v>
       </c>
       <c r="G10">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>46290</v>
-      </c>
       <c r="B11">
         <v>1010</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
       </c>
-      <c r="D11">
-        <v>1000</v>
-      </c>
       <c r="E11">
         <v>151000</v>
       </c>
@@ -776,22 +713,16 @@
         <v>69000</v>
       </c>
       <c r="G11">
-        <v>22000</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>46295</v>
-      </c>
       <c r="B12">
         <v>1011</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
-      <c r="D12">
-        <v>1000</v>
-      </c>
       <c r="E12">
         <v>59067</v>
       </c>
@@ -799,22 +730,16 @@
         <v>69000</v>
       </c>
       <c r="G12">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>46295</v>
-      </c>
       <c r="B13">
         <v>1012</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
-      <c r="D13">
-        <v>1000</v>
-      </c>
       <c r="E13">
         <v>153500</v>
       </c>
@@ -822,22 +747,16 @@
         <v>69000</v>
       </c>
       <c r="G13">
-        <v>100000</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>46290</v>
-      </c>
       <c r="B14">
         <v>1013</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="D14">
-        <v>1000</v>
-      </c>
       <c r="E14">
         <v>101759</v>
       </c>
@@ -845,22 +764,16 @@
         <v>69000</v>
       </c>
       <c r="G14">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>46291</v>
-      </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
-      <c r="D15">
-        <v>1000</v>
-      </c>
       <c r="E15">
         <v>102928</v>
       </c>
@@ -868,22 +781,16 @@
         <v>69000</v>
       </c>
       <c r="G15">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>46295</v>
-      </c>
       <c r="B16">
         <v>1015</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
-      <c r="D16">
-        <v>1000</v>
-      </c>
       <c r="E16">
         <v>184553</v>
       </c>
@@ -891,22 +798,16 @@
         <v>69000</v>
       </c>
       <c r="G16">
-        <v>103000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>46296</v>
-      </c>
+        <v>104000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>1016</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
-      <c r="D17">
-        <v>1000</v>
-      </c>
       <c r="E17">
         <v>54973</v>
       </c>
@@ -914,22 +815,16 @@
         <v>69000</v>
       </c>
       <c r="G17">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>46294</v>
-      </c>
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>1017</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
-      <c r="D18">
-        <v>1000</v>
-      </c>
       <c r="E18">
         <v>73327</v>
       </c>
@@ -937,22 +832,16 @@
         <v>69000</v>
       </c>
       <c r="G18">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>46286</v>
-      </c>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>1018</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
-      <c r="D19">
-        <v>1000</v>
-      </c>
       <c r="E19">
         <v>49125</v>
       </c>
@@ -960,22 +849,16 @@
         <v>69000</v>
       </c>
       <c r="G19">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>46291</v>
-      </c>
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>1019</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
-      <c r="D20">
-        <v>1000</v>
-      </c>
       <c r="E20">
         <v>0</v>
       </c>
@@ -983,22 +866,16 @@
         <v>69000</v>
       </c>
       <c r="G20">
-        <v>43000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>46295</v>
-      </c>
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
-      <c r="D21">
-        <v>1000</v>
-      </c>
       <c r="E21">
         <v>51464</v>
       </c>
@@ -1006,22 +883,16 @@
         <v>69000</v>
       </c>
       <c r="G21">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>46290</v>
-      </c>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>1021</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
-      <c r="D22">
-        <v>1000</v>
-      </c>
       <c r="E22">
         <v>0</v>
       </c>
@@ -1029,22 +900,16 @@
         <v>69000</v>
       </c>
       <c r="G22">
-        <v>41000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>46282</v>
-      </c>
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>1022</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
-      <c r="D23">
-        <v>1000</v>
-      </c>
       <c r="E23">
         <v>65500</v>
       </c>
@@ -1052,22 +917,16 @@
         <v>69000</v>
       </c>
       <c r="G23">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>46294</v>
-      </c>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>1023</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="D24">
-        <v>1000</v>
-      </c>
       <c r="E24">
         <v>53803</v>
       </c>
@@ -1075,22 +934,16 @@
         <v>69000</v>
       </c>
       <c r="G24">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>46296</v>
-      </c>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>1024</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
-      <c r="D25">
-        <v>1000</v>
-      </c>
       <c r="E25">
         <v>199000</v>
       </c>
@@ -1098,22 +951,16 @@
         <v>69000</v>
       </c>
       <c r="G25">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>46291</v>
-      </c>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>1025</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
-      <c r="D26">
-        <v>1000</v>
-      </c>
       <c r="E26">
         <v>49125</v>
       </c>
@@ -1121,22 +968,16 @@
         <v>69000</v>
       </c>
       <c r="G26">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>46294</v>
-      </c>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>1026</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
       </c>
-      <c r="D27">
-        <v>1000</v>
-      </c>
       <c r="E27">
         <v>51464</v>
       </c>
@@ -1144,22 +985,16 @@
         <v>69000</v>
       </c>
       <c r="G27">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>46291</v>
-      </c>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>1027</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
-      <c r="D28">
-        <v>1000</v>
-      </c>
       <c r="E28">
         <v>0</v>
       </c>
@@ -1167,22 +1002,16 @@
         <v>69000</v>
       </c>
       <c r="G28">
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>46290</v>
-      </c>
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>1028</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
-      <c r="D29">
-        <v>1000</v>
-      </c>
       <c r="E29">
         <v>0</v>
       </c>
@@ -1190,22 +1019,16 @@
         <v>69000</v>
       </c>
       <c r="G29">
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <v>46294</v>
-      </c>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>1029</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
-      <c r="D30">
-        <v>1000</v>
-      </c>
       <c r="E30">
         <v>0</v>
       </c>
@@ -1213,22 +1036,16 @@
         <v>69000</v>
       </c>
       <c r="G30">
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>1030</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
-      <c r="D31">
-        <v>1000</v>
-      </c>
       <c r="E31">
         <v>0</v>
       </c>
@@ -1236,22 +1053,16 @@
         <v>69000</v>
       </c>
       <c r="G31">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
-        <v>46291</v>
-      </c>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
         <v>39</v>
       </c>
-      <c r="D32">
-        <v>1000</v>
-      </c>
       <c r="E32">
         <v>0</v>
       </c>
@@ -1259,22 +1070,16 @@
         <v>69000</v>
       </c>
       <c r="G32">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
-        <v>46294</v>
-      </c>
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
         <v>37</v>
       </c>
-      <c r="D33">
-        <v>1000</v>
-      </c>
       <c r="E33">
         <v>0</v>
       </c>
@@ -1282,22 +1087,16 @@
         <v>69000</v>
       </c>
       <c r="G33">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
-        <v>46291</v>
-      </c>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
         <v>38</v>
       </c>
-      <c r="D34">
-        <v>1000</v>
-      </c>
       <c r="E34">
         <v>0</v>
       </c>
@@ -1305,7 +1104,7 @@
         <v>69000</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -801,7 +801,7 @@
         <v>104000</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>1016</v>
       </c>
@@ -818,7 +818,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>1017</v>
       </c>
@@ -835,7 +835,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>1018</v>
       </c>
@@ -852,7 +852,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>1019</v>
       </c>
@@ -869,7 +869,7 @@
         <v>44000</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>1020</v>
       </c>
@@ -886,7 +886,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>1021</v>
       </c>
@@ -903,7 +903,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>1022</v>
       </c>
@@ -920,7 +920,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>1023</v>
       </c>
@@ -937,7 +937,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>1024</v>
       </c>
@@ -954,7 +954,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>1025</v>
       </c>
@@ -971,7 +971,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>1026</v>
       </c>
@@ -988,7 +988,10 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>46325</v>
+      </c>
       <c r="B28">
         <v>1027</v>
       </c>
@@ -1005,7 +1008,7 @@
         <v>43000</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>1028</v>
       </c>
@@ -1022,7 +1025,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>1029</v>
       </c>
@@ -1039,7 +1042,7 @@
         <v>43000</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>1030</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>1031</v>
       </c>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -998,6 +998,9 @@
       <c r="C28" t="s">
         <v>33</v>
       </c>
+      <c r="D28">
+        <v>1000</v>
+      </c>
       <c r="E28">
         <v>0</v>
       </c>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -564,6 +564,9 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>46319</v>
+      </c>
       <c r="B3">
         <v>1002</v>
       </c>
@@ -836,6 +839,9 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>46319</v>
+      </c>
       <c r="B19">
         <v>1018</v>
       </c>
@@ -990,7 +996,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="B28">
         <v>1027</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -573,6 +573,9 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
+      <c r="D3">
+        <v>1000</v>
+      </c>
       <c r="E3">
         <v>151000</v>
       </c>
@@ -847,6 +850,9 @@
       </c>
       <c r="C19" t="s">
         <v>24</v>
+      </c>
+      <c r="D19">
+        <v>1000</v>
       </c>
       <c r="E19">
         <v>49125</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>business_date</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>Mullataa Qajeelaa</t>
+  </si>
+  <si>
+    <t>Waaqshumaa Dirribaa</t>
   </si>
 </sst>
 </file>
@@ -512,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" bestFit="1" customWidth="1"/>
@@ -587,11 +590,17 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>46320</v>
+      </c>
       <c r="B4">
         <v>1003</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
       </c>
       <c r="E4">
         <v>151000</v>
@@ -621,12 +630,18 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>46320</v>
+      </c>
       <c r="B6">
         <v>1005</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
       <c r="E6">
         <v>61406</v>
       </c>
@@ -634,7 +649,7 @@
         <v>69000</v>
       </c>
       <c r="G6">
-        <v>13000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -672,11 +687,17 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>46320</v>
+      </c>
       <c r="B9">
         <v>1008</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
+      </c>
+      <c r="D9">
+        <v>1000</v>
       </c>
       <c r="E9">
         <v>145036</v>
@@ -757,11 +778,17 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>46320</v>
+      </c>
       <c r="B14">
         <v>1013</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
+      </c>
+      <c r="D14">
+        <v>1000</v>
       </c>
       <c r="E14">
         <v>101759</v>
@@ -899,11 +926,17 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>46320</v>
+      </c>
       <c r="B22">
         <v>1021</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
+      </c>
+      <c r="D22">
+        <v>1000</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -984,11 +1017,17 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>46320</v>
+      </c>
       <c r="B27">
         <v>1026</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
+      </c>
+      <c r="D27">
+        <v>1000</v>
       </c>
       <c r="E27">
         <v>51464</v>
@@ -1075,12 +1114,18 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>46320</v>
+      </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
         <v>39</v>
       </c>
+      <c r="D32">
+        <v>1000</v>
+      </c>
       <c r="E32">
         <v>0</v>
       </c>
@@ -1091,7 +1136,7 @@
         <v>41000</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>1032</v>
       </c>
@@ -1108,7 +1153,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>1033</v>
       </c>
@@ -1123,6 +1168,23 @@
       </c>
       <c r="G34">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>46320</v>
+      </c>
+      <c r="B35">
+        <v>1034</v>
+      </c>
+      <c r="C35" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>69000</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>business_date</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>Waaqshumaa Dirribaa</t>
+  </si>
+  <si>
+    <t>Damee Xaafaa</t>
   </si>
 </sst>
 </file>
@@ -515,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" bestFit="1" customWidth="1"/>
@@ -550,11 +553,17 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>46321</v>
+      </c>
       <c r="B2">
         <v>1001</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
       </c>
       <c r="E2">
         <v>88893</v>
@@ -613,11 +622,17 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>46322</v>
+      </c>
       <c r="B5">
         <v>1004</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
+      </c>
+      <c r="D5">
+        <v>1000</v>
       </c>
       <c r="E5">
         <v>84553</v>
@@ -653,11 +668,17 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>46321</v>
+      </c>
       <c r="B7">
         <v>1006</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
+      </c>
+      <c r="D7">
+        <v>1000</v>
       </c>
       <c r="E7">
         <v>151000</v>
@@ -818,12 +839,18 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>46321</v>
+      </c>
       <c r="B16">
         <v>1015</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
+      <c r="D16">
+        <v>1000</v>
+      </c>
       <c r="E16">
         <v>184553</v>
       </c>
@@ -831,7 +858,7 @@
         <v>69000</v>
       </c>
       <c r="G16">
-        <v>104000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -892,11 +919,17 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>46321</v>
+      </c>
       <c r="B20">
         <v>1019</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
+      </c>
+      <c r="D20">
+        <v>1000</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -966,11 +999,17 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>46322</v>
+      </c>
       <c r="B24">
         <v>1023</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
+      </c>
+      <c r="D24">
+        <v>1000</v>
       </c>
       <c r="E24">
         <v>53803</v>
@@ -1063,11 +1102,17 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>46322</v>
+      </c>
       <c r="B29">
         <v>1028</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
+      </c>
+      <c r="D29">
+        <v>1000</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1185,6 +1230,29 @@
       </c>
       <c r="F35">
         <v>69000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <v>46321</v>
+      </c>
+      <c r="B36">
+        <v>1035</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36">
+        <v>1000</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>69000</v>
+      </c>
+      <c r="G36">
+        <v>39000</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>business_date</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>Damee Xaafaa</t>
+  </si>
+  <si>
+    <t>Margaa Jimaa</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" bestFit="1" customWidth="1"/>
@@ -879,11 +882,17 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>46322</v>
+      </c>
       <c r="B18">
         <v>1017</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
+      </c>
+      <c r="D18">
+        <v>1000</v>
       </c>
       <c r="E18">
         <v>73327</v>
@@ -1231,6 +1240,9 @@
       <c r="F35">
         <v>69000</v>
       </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
@@ -1253,6 +1265,29 @@
       </c>
       <c r="G36">
         <v>39000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>46322</v>
+      </c>
+      <c r="B37">
+        <v>1036</v>
+      </c>
+      <c r="C37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37">
+        <v>1000</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>69000</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -768,11 +768,17 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>46323</v>
+      </c>
       <c r="B12">
         <v>1011</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
+      </c>
+      <c r="D12">
+        <v>1000</v>
       </c>
       <c r="E12">
         <v>59067</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -751,11 +751,17 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>46323</v>
+      </c>
       <c r="B11">
         <v>1010</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
+      </c>
+      <c r="D11">
+        <v>1000</v>
       </c>
       <c r="E11">
         <v>151000</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -734,11 +734,17 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>46323</v>
+      </c>
       <c r="B10">
         <v>1009</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
+      </c>
+      <c r="D10">
+        <v>1000</v>
       </c>
       <c r="E10">
         <v>61406</v>
@@ -837,11 +843,17 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>46324</v>
+      </c>
       <c r="B15">
         <v>1014</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
+      </c>
+      <c r="D15">
+        <v>1000</v>
       </c>
       <c r="E15">
         <v>102928</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1072,11 +1072,17 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>46323</v>
+      </c>
       <c r="B26">
         <v>1025</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
+      </c>
+      <c r="D26">
+        <v>1000</v>
       </c>
       <c r="E26">
         <v>49125</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1238,11 +1238,17 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>46324</v>
+      </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
         <v>38</v>
+      </c>
+      <c r="D34">
+        <v>1000</v>
       </c>
       <c r="E34">
         <v>0</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -975,11 +975,17 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>46324</v>
+      </c>
       <c r="B21">
         <v>1020</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
+      </c>
+      <c r="D21">
+        <v>1000</v>
       </c>
       <c r="E21">
         <v>51464</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -803,11 +803,17 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>46325</v>
+      </c>
       <c r="B13">
         <v>1012</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
+      </c>
+      <c r="D13">
+        <v>1000</v>
       </c>
       <c r="E13">
         <v>153500</v>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1027,12 +1027,18 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>46325</v>
+      </c>
       <c r="B23">
         <v>1022</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
+      <c r="D23">
+        <v>1000</v>
+      </c>
       <c r="E23">
         <v>65500</v>
       </c>
@@ -1040,7 +1046,7 @@
         <v>69000</v>
       </c>
       <c r="G23">
-        <v>7000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>business_date</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>Margaa Jimaa</t>
+  </si>
+  <si>
+    <t>Biraanuu Gaaddisaa</t>
   </si>
 </sst>
 </file>
@@ -521,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.109375" style="3" bestFit="1" customWidth="1"/>
@@ -1344,6 +1347,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B38">
+        <v>1037</v>
+      </c>
+      <c r="C38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38">
+        <v>1000</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>69000</v>
+      </c>
+      <c r="G38">
+        <v>17000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/EGSA2026_27_Monthly_report.xlsx
+++ b/EGSA2026_27_Monthly_report.xlsx
@@ -1185,12 +1185,18 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>46325</v>
+      </c>
       <c r="B30">
         <v>1029</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
+      <c r="D30">
+        <v>1000</v>
+      </c>
       <c r="E30">
         <v>0</v>
       </c>
@@ -1202,11 +1208,17 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <v>46325</v>
+      </c>
       <c r="B31">
         <v>1030</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
+      </c>
+      <c r="D31">
+        <v>1000</v>
       </c>
       <c r="E31">
         <v>0</v>
